--- a/diseases/d124/2005-2009.xlsx
+++ b/diseases/d124/2005-2009.xlsx
@@ -2238,7 +2238,7 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN10" t="b">
@@ -3613,7 +3613,7 @@
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN18" t="b">
@@ -4988,7 +4988,7 @@
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN26" t="b">
@@ -6215,7 +6215,7 @@
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN33" t="b">
@@ -7590,7 +7590,7 @@
       </c>
       <c r="AM41" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN41" t="b">
@@ -8965,7 +8965,7 @@
       </c>
       <c r="AM49" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN49" t="b">
@@ -10340,7 +10340,7 @@
       </c>
       <c r="AM57" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN57" t="b">
@@ -11715,7 +11715,7 @@
       </c>
       <c r="AM65" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN65" t="b">
@@ -13090,7 +13090,7 @@
       </c>
       <c r="AM73" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN73" t="b">
@@ -14465,7 +14465,7 @@
       </c>
       <c r="AM81" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN81" t="b">
@@ -15840,7 +15840,7 @@
       </c>
       <c r="AM89" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN89" t="b">
@@ -17215,7 +17215,7 @@
       </c>
       <c r="AM97" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN97" t="b">
@@ -18983,7 +18983,7 @@
       </c>
       <c r="AM107" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN107" t="b">
@@ -20358,7 +20358,7 @@
       </c>
       <c r="AM115" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN115" t="b">
@@ -21733,7 +21733,7 @@
       </c>
       <c r="AM123" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN123" t="b">
@@ -23108,7 +23108,7 @@
       </c>
       <c r="AM131" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN131" t="b">
@@ -24483,7 +24483,7 @@
       </c>
       <c r="AM139" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN139" t="b">
@@ -25858,7 +25858,7 @@
       </c>
       <c r="AM147" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN147" t="b">
@@ -27233,7 +27233,7 @@
       </c>
       <c r="AM155" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN155" t="b">
@@ -28608,7 +28608,7 @@
       </c>
       <c r="AM163" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN163" t="b">
@@ -29983,7 +29983,7 @@
       </c>
       <c r="AM171" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN171" t="b">
@@ -31358,7 +31358,7 @@
       </c>
       <c r="AM179" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN179" t="b">
@@ -32733,7 +32733,7 @@
       </c>
       <c r="AM187" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN187" t="b">
@@ -34108,7 +34108,7 @@
       </c>
       <c r="AM195" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN195" t="b">
@@ -35876,7 +35876,7 @@
       </c>
       <c r="AM205" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN205" t="b">
@@ -37251,7 +37251,7 @@
       </c>
       <c r="AM213" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN213" t="b">
@@ -38478,7 +38478,7 @@
       </c>
       <c r="AM220" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN220" t="b">
@@ -39853,7 +39853,7 @@
       </c>
       <c r="AM228" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN228" t="b">
@@ -41228,7 +41228,7 @@
       </c>
       <c r="AM236" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN236" t="b">
@@ -42603,7 +42603,7 @@
       </c>
       <c r="AM244" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN244" t="b">
@@ -43978,7 +43978,7 @@
       </c>
       <c r="AM252" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN252" t="b">
@@ -45353,7 +45353,7 @@
       </c>
       <c r="AM260" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN260" t="b">
@@ -46728,7 +46728,7 @@
       </c>
       <c r="AM268" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN268" t="b">
@@ -48103,7 +48103,7 @@
       </c>
       <c r="AM276" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN276" t="b">
@@ -49478,7 +49478,7 @@
       </c>
       <c r="AM284" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN284" t="b">
@@ -50853,7 +50853,7 @@
       </c>
       <c r="AM292" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN292" t="b">
@@ -52769,7 +52769,7 @@
       </c>
       <c r="AM303" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN303" t="b">
@@ -54292,7 +54292,7 @@
       </c>
       <c r="AM312" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN312" t="b">
@@ -55815,7 +55815,7 @@
       </c>
       <c r="AM321" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN321" t="b">
@@ -57338,7 +57338,7 @@
       </c>
       <c r="AM330" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN330" t="b">
@@ -58861,7 +58861,7 @@
       </c>
       <c r="AM339" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN339" t="b">
@@ -60384,7 +60384,7 @@
       </c>
       <c r="AM348" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN348" t="b">
@@ -61907,7 +61907,7 @@
       </c>
       <c r="AM357" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN357" t="b">
@@ -63430,7 +63430,7 @@
       </c>
       <c r="AM366" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN366" t="b">
@@ -64953,7 +64953,7 @@
       </c>
       <c r="AM375" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN375" t="b">
@@ -66476,7 +66476,7 @@
       </c>
       <c r="AM384" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN384" t="b">
@@ -67851,7 +67851,7 @@
       </c>
       <c r="AM392" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN392" t="b">
@@ -69374,7 +69374,7 @@
       </c>
       <c r="AM401" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN401" t="b">
@@ -71290,7 +71290,7 @@
       </c>
       <c r="AM412" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN412" t="b">
@@ -72813,7 +72813,7 @@
       </c>
       <c r="AM421" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN421" t="b">
@@ -74336,7 +74336,7 @@
       </c>
       <c r="AM430" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN430" t="b">
@@ -75859,7 +75859,7 @@
       </c>
       <c r="AM439" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN439" t="b">
@@ -77382,7 +77382,7 @@
       </c>
       <c r="AM448" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN448" t="b">
@@ -78905,7 +78905,7 @@
       </c>
       <c r="AM457" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN457" t="b">
@@ -80428,7 +80428,7 @@
       </c>
       <c r="AM466" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN466" t="b">
@@ -81951,7 +81951,7 @@
       </c>
       <c r="AM475" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN475" t="b">
@@ -83474,7 +83474,7 @@
       </c>
       <c r="AM484" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN484" t="b">
@@ -84997,7 +84997,7 @@
       </c>
       <c r="AM493" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN493" t="b">
@@ -86520,7 +86520,7 @@
       </c>
       <c r="AM502" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN502" t="b">
@@ -88043,7 +88043,7 @@
       </c>
       <c r="AM511" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN511" t="b">
